--- a/IMB.L.xlsx
+++ b/IMB.L.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767A7E6D-D94F-4FF6-942C-41BEB4BFECEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676835CB-2051-4A7F-B3BD-09337C4C46E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{181FAD11-A2A4-461C-94B3-6DFDE084D96F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="112">
   <si>
     <t>Imperial Brands</t>
   </si>
@@ -246,9 +246,6 @@
     <t>120 Markets</t>
   </si>
   <si>
-    <t>CEO: Stefan Bomhard</t>
-  </si>
-  <si>
     <t>Balance Sheet</t>
   </si>
   <si>
@@ -364,6 +361,18 @@
   </si>
   <si>
     <t>Management</t>
+  </si>
+  <si>
+    <t>CEO</t>
+  </si>
+  <si>
+    <t>Lukas Paravinci</t>
+  </si>
+  <si>
+    <t>CFO</t>
+  </si>
+  <si>
+    <t>Murray McGowan</t>
   </si>
 </sst>
 </file>
@@ -873,13 +882,13 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="I2" s="3">
-        <v>32.01</v>
+        <v>32.61</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -887,7 +896,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="17">
-        <v>840.2</v>
+        <v>824.8</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>105</v>
@@ -902,7 +911,7 @@
       </c>
       <c r="I4" s="6">
         <f>I3*I2</f>
-        <v>26894.802</v>
+        <v>26896.727999999999</v>
       </c>
       <c r="J4" s="4"/>
     </row>
@@ -911,7 +920,7 @@
         <v>4</v>
       </c>
       <c r="I5" s="6">
-        <v>142</v>
+        <v>1439</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>105</v>
@@ -925,8 +934,8 @@
         <v>5</v>
       </c>
       <c r="I6" s="6">
-        <f>2766+7735</f>
-        <v>10501</v>
+        <f>1070+8524</f>
+        <v>9594</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>105</v>
@@ -938,7 +947,7 @@
       </c>
       <c r="I7" s="6">
         <f>I4-I5+I6</f>
-        <v>37253.801999999996</v>
+        <v>35051.728000000003</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -954,11 +963,11 @@
         <v>41</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I9" s="6">
         <f>I6-I5</f>
-        <v>10359</v>
+        <v>8155</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -977,7 +986,7 @@
         <v>66</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -988,7 +997,10 @@
         <v>66</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>69</v>
+        <v>108</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -997,6 +1009,12 @@
       </c>
       <c r="C13" s="2" t="s">
         <v>66</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1168,10 +1186,10 @@
         <v>21</v>
       </c>
       <c r="G2" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="23" t="s">
         <v>105</v>
-      </c>
-      <c r="H2" s="23" t="s">
-        <v>106</v>
       </c>
       <c r="J2" s="11" t="s">
         <v>10</v>
@@ -1195,7 +1213,7 @@
         <v>16</v>
       </c>
       <c r="Q2" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:57">
@@ -1252,7 +1270,10 @@
         <f>86.6+19.1+84.3</f>
         <v>190</v>
       </c>
-      <c r="Q3" s="12"/>
+      <c r="Q3" s="12">
+        <f>85.4+18+83.5</f>
+        <v>186.9</v>
+      </c>
       <c r="R3" s="12"/>
       <c r="S3" s="12"/>
       <c r="T3" s="12"/>
@@ -1378,7 +1399,9 @@
       <c r="N5" s="17"/>
       <c r="O5" s="17"/>
       <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
+      <c r="Q5" s="17">
+        <v>21503</v>
+      </c>
       <c r="R5" s="17"/>
       <c r="S5" s="17"/>
       <c r="T5" s="17"/>
@@ -1423,7 +1446,7 @@
     <row r="6" spans="1:57">
       <c r="A6" s="11"/>
       <c r="B6" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
@@ -1447,7 +1470,9 @@
       <c r="N6" s="17"/>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
+      <c r="Q6" s="17">
+        <v>11448</v>
+      </c>
       <c r="R6" s="17"/>
       <c r="S6" s="17"/>
       <c r="T6" s="17"/>
@@ -1533,7 +1558,9 @@
       <c r="P7" s="15">
         <v>32411</v>
       </c>
-      <c r="Q7" s="17"/>
+      <c r="Q7" s="15">
+        <v>32171</v>
+      </c>
       <c r="R7" s="17"/>
       <c r="S7" s="17"/>
       <c r="T7" s="17"/>
@@ -1619,7 +1646,9 @@
       <c r="P8" s="17">
         <v>13925</v>
       </c>
-      <c r="Q8" s="17"/>
+      <c r="Q8" s="17">
+        <v>13187</v>
+      </c>
       <c r="R8" s="17"/>
       <c r="S8" s="17"/>
       <c r="T8" s="17"/>
@@ -1705,7 +1734,9 @@
       <c r="P9" s="17">
         <v>11707</v>
       </c>
-      <c r="Q9" s="17"/>
+      <c r="Q9" s="17">
+        <v>11982</v>
+      </c>
       <c r="R9" s="17"/>
       <c r="S9" s="17"/>
       <c r="T9" s="17"/>
@@ -1774,7 +1805,7 @@
       <c r="H10" s="17"/>
       <c r="I10" s="17"/>
       <c r="J10" s="17">
-        <f t="shared" ref="J10:P10" si="2">J7-J8-J9</f>
+        <f t="shared" ref="J10:Q10" si="2">J7-J8-J9</f>
         <v>6010</v>
       </c>
       <c r="K10" s="17">
@@ -1801,7 +1832,10 @@
         <f t="shared" si="2"/>
         <v>6779</v>
       </c>
-      <c r="Q10" s="17"/>
+      <c r="Q10" s="17">
+        <f t="shared" si="2"/>
+        <v>7002</v>
+      </c>
       <c r="R10" s="17"/>
       <c r="S10" s="17"/>
       <c r="T10" s="17"/>
@@ -1887,7 +1921,9 @@
       <c r="P11" s="17">
         <v>2383</v>
       </c>
-      <c r="Q11" s="17"/>
+      <c r="Q11" s="17">
+        <v>2469</v>
+      </c>
       <c r="R11" s="17"/>
       <c r="S11" s="17"/>
       <c r="T11" s="17"/>
@@ -1973,7 +2009,9 @@
       <c r="P12" s="17">
         <v>842</v>
       </c>
-      <c r="Q12" s="17"/>
+      <c r="Q12" s="17">
+        <v>1043</v>
+      </c>
       <c r="R12" s="17"/>
       <c r="S12" s="17"/>
       <c r="T12" s="17"/>
@@ -2066,10 +2104,13 @@
         <v>3402</v>
       </c>
       <c r="P13" s="17">
-        <f t="shared" ref="P13" si="12">P10-P11-P12</f>
+        <f t="shared" ref="P13:Q13" si="12">P10-P11-P12</f>
         <v>3554</v>
       </c>
-      <c r="Q13" s="17"/>
+      <c r="Q13" s="17">
+        <f t="shared" si="12"/>
+        <v>3490</v>
+      </c>
       <c r="R13" s="17"/>
       <c r="S13" s="17"/>
       <c r="T13" s="17"/>
@@ -2165,7 +2206,10 @@
         <f>560-1094+9</f>
         <v>-525</v>
       </c>
-      <c r="Q14" s="17"/>
+      <c r="Q14" s="17">
+        <f>-374+12</f>
+        <v>-362</v>
+      </c>
       <c r="R14" s="17"/>
       <c r="S14" s="17"/>
       <c r="T14" s="17"/>
@@ -2209,7 +2253,7 @@
     </row>
     <row r="15" spans="1:57">
       <c r="B15" s="22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C15" s="17">
         <f>C13+C14</f>
@@ -2258,10 +2302,13 @@
         <v>3111</v>
       </c>
       <c r="P15" s="17">
-        <f t="shared" ref="P15" si="20">P13+P14</f>
+        <f t="shared" ref="P15:Q15" si="20">P13+P14</f>
         <v>3029</v>
       </c>
-      <c r="Q15" s="17"/>
+      <c r="Q15" s="17">
+        <f t="shared" si="20"/>
+        <v>3128</v>
+      </c>
       <c r="R15" s="17"/>
       <c r="S15" s="17"/>
       <c r="T15" s="17"/>
@@ -2347,7 +2394,9 @@
       <c r="P16" s="17">
         <v>282</v>
       </c>
-      <c r="Q16" s="17"/>
+      <c r="Q16" s="17">
+        <v>908</v>
+      </c>
       <c r="R16" s="17"/>
       <c r="S16" s="17"/>
       <c r="T16" s="17"/>
@@ -2416,7 +2465,7 @@
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
       <c r="J17" s="17">
-        <f t="shared" ref="J17:P17" si="22">J15-J16</f>
+        <f t="shared" ref="J17:Q17" si="22">J15-J16</f>
         <v>1427</v>
       </c>
       <c r="K17" s="17">
@@ -2443,7 +2492,10 @@
         <f t="shared" si="22"/>
         <v>2747</v>
       </c>
-      <c r="Q17" s="17"/>
+      <c r="Q17" s="17">
+        <f t="shared" si="22"/>
+        <v>2220</v>
+      </c>
       <c r="R17" s="17"/>
       <c r="S17" s="17"/>
       <c r="T17" s="17"/>
@@ -2529,7 +2581,9 @@
       <c r="P18" s="17">
         <v>134</v>
       </c>
-      <c r="Q18" s="17"/>
+      <c r="Q18" s="17">
+        <v>149</v>
+      </c>
       <c r="R18" s="17"/>
       <c r="S18" s="17"/>
       <c r="T18" s="17"/>
@@ -2598,7 +2652,7 @@
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
       <c r="J19" s="17">
-        <f t="shared" ref="J19:P19" si="24">J17-J18</f>
+        <f t="shared" ref="J19:Q19" si="24">J17-J18</f>
         <v>1368</v>
       </c>
       <c r="K19" s="17">
@@ -2625,7 +2679,10 @@
         <f t="shared" si="24"/>
         <v>2613</v>
       </c>
-      <c r="Q19" s="17"/>
+      <c r="Q19" s="17">
+        <f t="shared" si="24"/>
+        <v>2071</v>
+      </c>
       <c r="R19" s="17"/>
       <c r="S19" s="17"/>
       <c r="T19" s="17"/>
@@ -2736,8 +2793,8 @@
         <v>0.96</v>
       </c>
       <c r="F21" s="18">
-        <f t="shared" ref="F21:G21" si="25">+P21-E21</f>
-        <v>2.0470000000000002</v>
+        <f t="shared" ref="F21" si="25">+P21-E21</f>
+        <v>2.0469044879171463</v>
       </c>
       <c r="G21" s="18">
         <f>+G19/G22</f>
@@ -2763,10 +2820,14 @@
       <c r="O21" s="18">
         <v>2.524</v>
       </c>
-      <c r="P21" s="17">
-        <v>3.0070000000000001</v>
-      </c>
-      <c r="Q21" s="17"/>
+      <c r="P21" s="18">
+        <f>+P19/P22</f>
+        <v>3.0069044879171463</v>
+      </c>
+      <c r="Q21" s="18">
+        <f>+Q19/Q22</f>
+        <v>2.5109117361784676</v>
+      </c>
       <c r="R21" s="17"/>
       <c r="S21" s="17"/>
       <c r="T21" s="17"/>
@@ -2826,7 +2887,7 @@
       </c>
       <c r="F22" s="17">
         <f>F19/F21</f>
-        <v>863.21446018563745</v>
+        <v>863.2547392565607</v>
       </c>
       <c r="G22" s="17">
         <v>840.2</v>
@@ -2858,10 +2919,11 @@
         <v>922.34548335974648</v>
       </c>
       <c r="P22" s="17">
-        <f t="shared" si="27"/>
-        <v>868.97239773860986</v>
-      </c>
-      <c r="Q22" s="17"/>
+        <v>869</v>
+      </c>
+      <c r="Q22" s="17">
+        <v>824.8</v>
+      </c>
       <c r="R22" s="17"/>
       <c r="S22" s="17"/>
       <c r="T22" s="17"/>
@@ -2962,7 +3024,7 @@
     </row>
     <row r="24" spans="1:57">
       <c r="B24" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -2985,7 +3047,7 @@
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="K24" s="19">
-        <f t="shared" ref="K24:P24" si="30">+K3/J3-1</f>
+        <f t="shared" ref="K24:Q24" si="30">+K3/J3-1</f>
         <v>-4.4227005870841496E-2</v>
       </c>
       <c r="L24" s="19">
@@ -3008,7 +3070,10 @@
         <f t="shared" si="30"/>
         <v>-4.0404040404040442E-2</v>
       </c>
-      <c r="Q24" s="17"/>
+      <c r="Q24" s="19">
+        <f t="shared" si="30"/>
+        <v>-1.6315789473684172E-2</v>
+      </c>
       <c r="R24" s="17"/>
       <c r="S24" s="17"/>
       <c r="T24" s="17"/>
@@ -3098,7 +3163,10 @@
         <f>P7/O7-1</f>
         <v>-1.9707467282524815E-3</v>
       </c>
-      <c r="Q25" s="15"/>
+      <c r="Q25" s="24">
+        <f>Q7/P7-1</f>
+        <v>-7.4048934003887457E-3</v>
+      </c>
       <c r="R25" s="15"/>
       <c r="S25" s="15"/>
       <c r="T25" s="15"/>
@@ -3197,7 +3265,10 @@
         <f t="shared" si="37"/>
         <v>0.20915738483848076</v>
       </c>
-      <c r="Q26" s="17"/>
+      <c r="Q26" s="19">
+        <f t="shared" ref="Q26" si="38">Q10/Q7</f>
+        <v>0.21764943582729787</v>
+      </c>
       <c r="R26" s="17"/>
       <c r="S26" s="17"/>
       <c r="T26" s="17"/>
@@ -3244,11 +3315,11 @@
         <v>38</v>
       </c>
       <c r="C27" s="19">
-        <f t="shared" ref="C27:D27" si="38">C13/C7</f>
+        <f t="shared" ref="C27:D27" si="39">C13/C7</f>
         <v>9.9539290117448581E-2</v>
       </c>
       <c r="D27" s="19">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.10947022972339428</v>
       </c>
       <c r="E27" s="19">
@@ -3256,47 +3327,50 @@
         <v>9.9176845459373345E-2</v>
       </c>
       <c r="F27" s="19">
-        <f t="shared" ref="F27:G27" si="39">F13/F7</f>
+        <f t="shared" ref="F27:G27" si="40">F13/F7</f>
         <v>0.11875252204992218</v>
       </c>
       <c r="G27" s="19">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>9.9698712681457136E-2</v>
       </c>
       <c r="H27" s="19" t="e">
-        <f t="shared" ref="H27" si="40">H13/H7</f>
+        <f t="shared" ref="H27" si="41">H13/H7</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I27" s="17"/>
       <c r="J27" s="19">
-        <f t="shared" ref="J27:P27" si="41">J13/J7</f>
+        <f t="shared" ref="J27:P27" si="42">J13/J7</f>
         <v>8.005720747688419E-2</v>
       </c>
       <c r="K27" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>6.9538519972146606E-2</v>
       </c>
       <c r="L27" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>8.3870769608746398E-2</v>
       </c>
       <c r="M27" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>9.5940959409594101E-2</v>
       </c>
       <c r="N27" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>8.2424503087462755E-2</v>
       </c>
       <c r="O27" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.10475750577367206</v>
       </c>
       <c r="P27" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.10965412977075684</v>
       </c>
-      <c r="Q27" s="17"/>
+      <c r="Q27" s="19">
+        <f t="shared" ref="Q27" si="43">Q13/Q7</f>
+        <v>0.10848279506387741</v>
+      </c>
       <c r="R27" s="17"/>
       <c r="S27" s="17"/>
       <c r="T27" s="17"/>
@@ -3343,11 +3417,11 @@
         <v>39</v>
       </c>
       <c r="C28" s="19">
-        <f t="shared" ref="C28:D28" si="42">C16/C15</f>
+        <f t="shared" ref="C28:D28" si="44">C16/C15</f>
         <v>0.19196119196119196</v>
       </c>
       <c r="D28" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0.22661870503597123</v>
       </c>
       <c r="E28" s="19">
@@ -3359,43 +3433,46 @@
         <v>2.8116710875331564E-2</v>
       </c>
       <c r="G28" s="19">
-        <f t="shared" ref="G28:H28" si="43">G16/G15</f>
+        <f t="shared" ref="G28:H28" si="45">G16/G15</f>
         <v>0.31741140215716485</v>
       </c>
       <c r="H28" s="19" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I28" s="17"/>
       <c r="J28" s="19">
-        <f t="shared" ref="J28:P28" si="44">J16/J15</f>
+        <f t="shared" ref="J28:P28" si="46">J16/J15</f>
         <v>0.2172243554580362</v>
       </c>
       <c r="K28" s="19">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.36035502958579879</v>
       </c>
       <c r="L28" s="19">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.2807017543859649</v>
       </c>
       <c r="M28" s="19">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.10222359481161211</v>
       </c>
       <c r="N28" s="19">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.34731477851822817</v>
       </c>
       <c r="O28" s="19">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.21054323368691738</v>
       </c>
       <c r="P28" s="19">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>9.3100033014196101E-2</v>
       </c>
-      <c r="Q28" s="17"/>
+      <c r="Q28" s="19">
+        <f t="shared" ref="Q28" si="47">Q16/Q15</f>
+        <v>0.29028132992327366</v>
+      </c>
       <c r="R28" s="17"/>
       <c r="S28" s="17"/>
       <c r="T28" s="17"/>
@@ -3499,7 +3576,7 @@
         <v>9</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -3559,7 +3636,7 @@
     </row>
     <row r="31" spans="1:57">
       <c r="B31" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
@@ -3589,7 +3666,9 @@
       <c r="P31" s="17">
         <v>15938</v>
       </c>
-      <c r="Q31" s="17"/>
+      <c r="Q31" s="17">
+        <v>16208</v>
+      </c>
       <c r="R31" s="17"/>
       <c r="S31" s="17"/>
       <c r="T31" s="17"/>
@@ -3633,7 +3712,7 @@
     </row>
     <row r="32" spans="1:57">
       <c r="B32" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -3663,7 +3742,9 @@
       <c r="P32" s="17">
         <v>1561</v>
       </c>
-      <c r="Q32" s="17"/>
+      <c r="Q32" s="17">
+        <v>1524</v>
+      </c>
       <c r="R32" s="17"/>
       <c r="S32" s="17"/>
       <c r="T32" s="17"/>
@@ -3707,7 +3788,7 @@
     </row>
     <row r="33" spans="2:57">
       <c r="B33" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
@@ -3737,7 +3818,9 @@
       <c r="P33" s="17">
         <v>262</v>
       </c>
-      <c r="Q33" s="17"/>
+      <c r="Q33" s="17">
+        <v>373</v>
+      </c>
       <c r="R33" s="17"/>
       <c r="S33" s="17"/>
       <c r="T33" s="17"/>
@@ -3781,7 +3864,7 @@
     </row>
     <row r="34" spans="2:57">
       <c r="B34" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
@@ -3811,7 +3894,9 @@
       <c r="P34" s="17">
         <v>56</v>
       </c>
-      <c r="Q34" s="17"/>
+      <c r="Q34" s="17">
+        <v>66</v>
+      </c>
       <c r="R34" s="17"/>
       <c r="S34" s="17"/>
       <c r="T34" s="17"/>
@@ -3855,7 +3940,7 @@
     </row>
     <row r="35" spans="2:57">
       <c r="B35" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
@@ -3885,7 +3970,9 @@
       <c r="P35" s="17">
         <v>376</v>
       </c>
-      <c r="Q35" s="17"/>
+      <c r="Q35" s="17">
+        <v>314</v>
+      </c>
       <c r="R35" s="17"/>
       <c r="S35" s="17"/>
       <c r="T35" s="17"/>
@@ -3929,7 +4016,7 @@
     </row>
     <row r="36" spans="2:57">
       <c r="B36" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
@@ -3959,7 +4046,9 @@
       <c r="P36" s="17">
         <v>118</v>
       </c>
-      <c r="Q36" s="17"/>
+      <c r="Q36" s="17">
+        <v>133</v>
+      </c>
       <c r="R36" s="17"/>
       <c r="S36" s="17"/>
       <c r="T36" s="17"/>
@@ -4003,7 +4092,7 @@
     </row>
     <row r="37" spans="2:57">
       <c r="B37" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
@@ -4033,7 +4122,9 @@
       <c r="P37" s="17">
         <v>330</v>
       </c>
-      <c r="Q37" s="17"/>
+      <c r="Q37" s="17">
+        <v>392</v>
+      </c>
       <c r="R37" s="17"/>
       <c r="S37" s="17"/>
       <c r="T37" s="17"/>
@@ -4077,7 +4168,7 @@
     </row>
     <row r="38" spans="2:57">
       <c r="B38" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
@@ -4108,7 +4199,9 @@
       <c r="P38" s="17">
         <v>889</v>
       </c>
-      <c r="Q38" s="17"/>
+      <c r="Q38" s="17">
+        <v>893</v>
+      </c>
       <c r="R38" s="17"/>
       <c r="S38" s="17"/>
       <c r="T38" s="17"/>
@@ -4152,7 +4245,7 @@
     </row>
     <row r="39" spans="2:57">
       <c r="B39" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C39" s="17"/>
       <c r="D39" s="17"/>
@@ -4162,23 +4255,23 @@
       <c r="H39" s="17"/>
       <c r="I39" s="17"/>
       <c r="J39" s="15">
-        <f t="shared" ref="J39:N39" si="45">SUM(J31:J38)</f>
+        <f t="shared" ref="J39:N39" si="48">SUM(J31:J38)</f>
         <v>23595</v>
       </c>
       <c r="K39" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>22642</v>
       </c>
       <c r="L39" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>22660</v>
       </c>
       <c r="M39" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>20883</v>
       </c>
       <c r="N39" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>22037</v>
       </c>
       <c r="O39" s="15">
@@ -4189,7 +4282,10 @@
         <f>SUM(P31:P38)</f>
         <v>19530</v>
       </c>
-      <c r="Q39" s="17"/>
+      <c r="Q39" s="15">
+        <f>SUM(Q31:Q38)</f>
+        <v>19903</v>
+      </c>
       <c r="R39" s="17"/>
       <c r="S39" s="17"/>
       <c r="T39" s="17"/>
@@ -4233,7 +4329,7 @@
     </row>
     <row r="40" spans="2:57">
       <c r="B40" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
@@ -4263,7 +4359,9 @@
       <c r="P40" s="17">
         <v>4080</v>
       </c>
-      <c r="Q40" s="17"/>
+      <c r="Q40" s="17">
+        <v>4466</v>
+      </c>
       <c r="R40" s="17"/>
       <c r="S40" s="17"/>
       <c r="T40" s="17"/>
@@ -4307,7 +4405,7 @@
     </row>
     <row r="41" spans="2:57">
       <c r="B41" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C41" s="17"/>
       <c r="D41" s="17"/>
@@ -4337,7 +4435,9 @@
       <c r="P41" s="17">
         <v>2645</v>
       </c>
-      <c r="Q41" s="17"/>
+      <c r="Q41" s="17">
+        <v>2716</v>
+      </c>
       <c r="R41" s="17"/>
       <c r="S41" s="17"/>
       <c r="T41" s="17"/>
@@ -4381,7 +4481,7 @@
     </row>
     <row r="42" spans="2:57">
       <c r="B42" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C42" s="17"/>
       <c r="D42" s="17"/>
@@ -4411,7 +4511,9 @@
       <c r="P42" s="17">
         <v>249</v>
       </c>
-      <c r="Q42" s="17"/>
+      <c r="Q42" s="17">
+        <v>146</v>
+      </c>
       <c r="R42" s="17"/>
       <c r="S42" s="17"/>
       <c r="T42" s="17"/>
@@ -4455,7 +4557,7 @@
     </row>
     <row r="43" spans="2:57">
       <c r="B43" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C43" s="17"/>
       <c r="D43" s="17"/>
@@ -4485,7 +4587,9 @@
       <c r="P43" s="17">
         <v>1078</v>
       </c>
-      <c r="Q43" s="17"/>
+      <c r="Q43" s="17">
+        <v>1439</v>
+      </c>
       <c r="R43" s="17"/>
       <c r="S43" s="17"/>
       <c r="T43" s="17"/>
@@ -4529,7 +4633,7 @@
     </row>
     <row r="44" spans="2:57">
       <c r="B44" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C44" s="17"/>
       <c r="D44" s="17"/>
@@ -4559,7 +4663,9 @@
       <c r="P44" s="17">
         <v>144</v>
       </c>
-      <c r="Q44" s="17"/>
+      <c r="Q44" s="17">
+        <v>45</v>
+      </c>
       <c r="R44" s="17"/>
       <c r="S44" s="17"/>
       <c r="T44" s="17"/>
@@ -4603,7 +4709,7 @@
     </row>
     <row r="45" spans="2:57">
       <c r="B45" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C45" s="17"/>
       <c r="D45" s="17"/>
@@ -4633,7 +4739,9 @@
       <c r="P45" s="17">
         <v>0</v>
       </c>
-      <c r="Q45" s="17"/>
+      <c r="Q45" s="17">
+        <v>0</v>
+      </c>
       <c r="R45" s="17"/>
       <c r="S45" s="17"/>
       <c r="T45" s="17"/>
@@ -4677,7 +4785,7 @@
     </row>
     <row r="46" spans="2:57">
       <c r="B46" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C46" s="17"/>
       <c r="D46" s="17"/>
@@ -4687,23 +4795,23 @@
       <c r="H46" s="17"/>
       <c r="I46" s="17"/>
       <c r="J46" s="15">
-        <f t="shared" ref="J46:N46" si="46">SUM(J40:J45)</f>
+        <f t="shared" ref="J46:N46" si="49">SUM(J40:J45)</f>
         <v>7253</v>
       </c>
       <c r="K46" s="15">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>11088</v>
       </c>
       <c r="L46" s="15">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>9650</v>
       </c>
       <c r="M46" s="15">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>8207</v>
       </c>
       <c r="N46" s="15">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>8921</v>
       </c>
       <c r="O46" s="15">
@@ -4714,7 +4822,10 @@
         <f>SUM(P40:P45)</f>
         <v>8196</v>
       </c>
-      <c r="Q46" s="17"/>
+      <c r="Q46" s="15">
+        <f>SUM(Q40:Q45)</f>
+        <v>8812</v>
+      </c>
       <c r="R46" s="17"/>
       <c r="S46" s="17"/>
       <c r="T46" s="17"/>
@@ -4815,7 +4926,7 @@
     </row>
     <row r="48" spans="2:57">
       <c r="B48" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C48" s="17"/>
       <c r="D48" s="17"/>
@@ -4825,23 +4936,23 @@
       <c r="H48" s="17"/>
       <c r="I48" s="17"/>
       <c r="J48" s="15">
-        <f t="shared" ref="J48:N48" si="47">J39+J46</f>
+        <f t="shared" ref="J48:N48" si="50">J39+J46</f>
         <v>30848</v>
       </c>
       <c r="K48" s="15">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>33730</v>
       </c>
       <c r="L48" s="15">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>32310</v>
       </c>
       <c r="M48" s="15">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>29090</v>
       </c>
       <c r="N48" s="15">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>30958</v>
       </c>
       <c r="O48" s="15">
@@ -4852,7 +4963,10 @@
         <f>P39+P46</f>
         <v>27726</v>
       </c>
-      <c r="Q48" s="17"/>
+      <c r="Q48" s="15">
+        <f>Q39+Q46</f>
+        <v>28715</v>
+      </c>
       <c r="R48" s="17"/>
       <c r="S48" s="17"/>
       <c r="T48" s="17"/>
@@ -4953,7 +5067,7 @@
     </row>
     <row r="50" spans="2:57">
       <c r="B50" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C50" s="17"/>
       <c r="D50" s="17"/>
@@ -4983,7 +5097,9 @@
       <c r="P50" s="17">
         <v>1191</v>
       </c>
-      <c r="Q50" s="17"/>
+      <c r="Q50" s="17">
+        <v>1070</v>
+      </c>
       <c r="R50" s="17"/>
       <c r="S50" s="17"/>
       <c r="T50" s="17"/>
@@ -5027,7 +5143,7 @@
     </row>
     <row r="51" spans="2:57">
       <c r="B51" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C51" s="17"/>
       <c r="D51" s="17"/>
@@ -5057,7 +5173,9 @@
       <c r="P51" s="17">
         <v>187</v>
       </c>
-      <c r="Q51" s="17"/>
+      <c r="Q51" s="17">
+        <v>28</v>
+      </c>
       <c r="R51" s="17"/>
       <c r="S51" s="17"/>
       <c r="T51" s="17"/>
@@ -5101,7 +5219,7 @@
     </row>
     <row r="52" spans="2:57">
       <c r="B52" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C52" s="17"/>
       <c r="D52" s="17"/>
@@ -5131,7 +5249,9 @@
       <c r="P52" s="17">
         <v>86</v>
       </c>
-      <c r="Q52" s="17"/>
+      <c r="Q52" s="17">
+        <v>89</v>
+      </c>
       <c r="R52" s="17"/>
       <c r="S52" s="17"/>
       <c r="T52" s="17"/>
@@ -5175,7 +5295,7 @@
     </row>
     <row r="53" spans="2:57">
       <c r="B53" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C53" s="17"/>
       <c r="D53" s="17"/>
@@ -5205,7 +5325,9 @@
       <c r="P53" s="17">
         <v>9497</v>
       </c>
-      <c r="Q53" s="17"/>
+      <c r="Q53" s="17">
+        <v>10040</v>
+      </c>
       <c r="R53" s="17"/>
       <c r="S53" s="17"/>
       <c r="T53" s="17"/>
@@ -5249,7 +5371,7 @@
     </row>
     <row r="54" spans="2:57">
       <c r="B54" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C54" s="17"/>
       <c r="D54" s="17"/>
@@ -5279,7 +5401,9 @@
       <c r="P54" s="17">
         <v>412</v>
       </c>
-      <c r="Q54" s="17"/>
+      <c r="Q54" s="17">
+        <v>572</v>
+      </c>
       <c r="R54" s="17"/>
       <c r="S54" s="17"/>
       <c r="T54" s="17"/>
@@ -5323,7 +5447,7 @@
     </row>
     <row r="55" spans="2:57">
       <c r="B55" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C55" s="17"/>
       <c r="D55" s="17"/>
@@ -5353,7 +5477,9 @@
       <c r="P55" s="17">
         <v>89</v>
       </c>
-      <c r="Q55" s="17"/>
+      <c r="Q55" s="17">
+        <v>55</v>
+      </c>
       <c r="R55" s="17"/>
       <c r="S55" s="17"/>
       <c r="T55" s="17"/>
@@ -5397,7 +5523,7 @@
     </row>
     <row r="56" spans="2:57">
       <c r="B56" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C56" s="17"/>
       <c r="D56" s="17"/>
@@ -5425,7 +5551,9 @@
       <c r="P56" s="17">
         <v>0</v>
       </c>
-      <c r="Q56" s="17"/>
+      <c r="Q56" s="17">
+        <v>0</v>
+      </c>
       <c r="R56" s="17"/>
       <c r="S56" s="17"/>
       <c r="T56" s="17"/>
@@ -5469,7 +5597,7 @@
     </row>
     <row r="57" spans="2:57">
       <c r="B57" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C57" s="17"/>
       <c r="D57" s="17"/>
@@ -5479,34 +5607,37 @@
       <c r="H57" s="17"/>
       <c r="I57" s="17"/>
       <c r="J57" s="15">
-        <f t="shared" ref="J57:O57" si="48">SUM(J50:J56)</f>
+        <f t="shared" ref="J57:O57" si="51">SUM(J50:J56)</f>
         <v>11237</v>
       </c>
       <c r="K57" s="15">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>12382</v>
       </c>
       <c r="L57" s="15">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>12325</v>
       </c>
       <c r="M57" s="15">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>10808</v>
       </c>
       <c r="N57" s="15">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>11139</v>
       </c>
       <c r="O57" s="15">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>11899</v>
       </c>
       <c r="P57" s="15">
         <f>SUM(P50:P56)</f>
         <v>11462</v>
       </c>
-      <c r="Q57" s="17"/>
+      <c r="Q57" s="15">
+        <f>SUM(Q50:Q56)</f>
+        <v>11854</v>
+      </c>
       <c r="R57" s="17"/>
       <c r="S57" s="17"/>
       <c r="T57" s="17"/>
@@ -5607,7 +5738,7 @@
     </row>
     <row r="59" spans="2:57">
       <c r="B59" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C59" s="17"/>
       <c r="D59" s="17"/>
@@ -5637,7 +5768,9 @@
       <c r="P59" s="17">
         <v>7606</v>
       </c>
-      <c r="Q59" s="17"/>
+      <c r="Q59" s="17">
+        <v>8524</v>
+      </c>
       <c r="R59" s="17"/>
       <c r="S59" s="17"/>
       <c r="T59" s="17"/>
@@ -5681,7 +5814,7 @@
     </row>
     <row r="60" spans="2:57">
       <c r="B60" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C60" s="17"/>
       <c r="D60" s="17"/>
@@ -5711,7 +5844,9 @@
       <c r="P60" s="17">
         <v>622</v>
       </c>
-      <c r="Q60" s="17"/>
+      <c r="Q60" s="17">
+        <v>806</v>
+      </c>
       <c r="R60" s="17"/>
       <c r="S60" s="17"/>
       <c r="T60" s="17"/>
@@ -5755,7 +5890,7 @@
     </row>
     <row r="61" spans="2:57">
       <c r="B61" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C61" s="17"/>
       <c r="D61" s="17"/>
@@ -5785,7 +5920,9 @@
       <c r="P61" s="17">
         <v>300</v>
       </c>
-      <c r="Q61" s="17"/>
+      <c r="Q61" s="17">
+        <v>313</v>
+      </c>
       <c r="R61" s="17"/>
       <c r="S61" s="17"/>
       <c r="T61" s="17"/>
@@ -5829,7 +5966,7 @@
     </row>
     <row r="62" spans="2:57">
       <c r="B62" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C62" s="17"/>
       <c r="D62" s="17"/>
@@ -5859,7 +5996,9 @@
       <c r="P62" s="17">
         <v>86</v>
       </c>
-      <c r="Q62" s="17"/>
+      <c r="Q62" s="17">
+        <v>41</v>
+      </c>
       <c r="R62" s="17"/>
       <c r="S62" s="17"/>
       <c r="T62" s="17"/>
@@ -5903,7 +6042,7 @@
     </row>
     <row r="63" spans="2:57">
       <c r="B63" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
@@ -5933,7 +6072,9 @@
       <c r="P63" s="17">
         <v>780</v>
       </c>
-      <c r="Q63" s="17"/>
+      <c r="Q63" s="17">
+        <v>747</v>
+      </c>
       <c r="R63" s="17"/>
       <c r="S63" s="17"/>
       <c r="T63" s="17"/>
@@ -5977,7 +6118,7 @@
     </row>
     <row r="64" spans="2:57">
       <c r="B64" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C64" s="17"/>
       <c r="D64" s="17"/>
@@ -6007,7 +6148,9 @@
       <c r="P64" s="17">
         <v>819</v>
       </c>
-      <c r="Q64" s="17"/>
+      <c r="Q64" s="17">
+        <v>801</v>
+      </c>
       <c r="R64" s="17"/>
       <c r="S64" s="17"/>
       <c r="T64" s="17"/>
@@ -6051,7 +6194,7 @@
     </row>
     <row r="65" spans="2:57">
       <c r="B65" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C65" s="17"/>
       <c r="D65" s="17"/>
@@ -6081,7 +6224,9 @@
       <c r="P65" s="17">
         <v>222</v>
       </c>
-      <c r="Q65" s="17"/>
+      <c r="Q65" s="17">
+        <v>197</v>
+      </c>
       <c r="R65" s="17"/>
       <c r="S65" s="17"/>
       <c r="T65" s="17"/>
@@ -6125,7 +6270,7 @@
     </row>
     <row r="66" spans="2:57">
       <c r="B66" s="14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C66" s="17"/>
       <c r="D66" s="17"/>
@@ -6135,23 +6280,23 @@
       <c r="H66" s="17"/>
       <c r="I66" s="17"/>
       <c r="J66" s="15">
-        <f t="shared" ref="J66:N66" si="49">SUM(J59:J65)</f>
+        <f t="shared" ref="J66:N66" si="52">SUM(J59:J65)</f>
         <v>13166</v>
       </c>
       <c r="K66" s="15">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>15764</v>
       </c>
       <c r="L66" s="15">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>14467</v>
       </c>
       <c r="M66" s="15">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>12342</v>
       </c>
       <c r="N66" s="15">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>12346</v>
       </c>
       <c r="O66" s="15">
@@ -6162,7 +6307,10 @@
         <f>SUM(P59:P65)</f>
         <v>10435</v>
       </c>
-      <c r="Q66" s="17"/>
+      <c r="Q66" s="15">
+        <f>SUM(Q59:Q65)</f>
+        <v>11429</v>
+      </c>
       <c r="R66" s="17"/>
       <c r="S66" s="17"/>
       <c r="T66" s="17"/>
@@ -6263,7 +6411,7 @@
     </row>
     <row r="68" spans="2:57">
       <c r="B68" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C68" s="17"/>
       <c r="D68" s="17"/>
@@ -6293,7 +6441,9 @@
       <c r="P68" s="17">
         <v>6029</v>
       </c>
-      <c r="Q68" s="17"/>
+      <c r="Q68" s="17">
+        <v>5432</v>
+      </c>
       <c r="R68" s="17"/>
       <c r="S68" s="17"/>
       <c r="T68" s="17"/>
@@ -6393,8 +6543,8 @@
       <c r="BE69" s="12"/>
     </row>
     <row r="70" spans="2:57">
-      <c r="B70" s="10" t="s">
-        <v>97</v>
+      <c r="B70" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="C70" s="17"/>
       <c r="D70" s="17"/>
@@ -6404,23 +6554,23 @@
       <c r="H70" s="17"/>
       <c r="I70" s="17"/>
       <c r="J70" s="15">
-        <f t="shared" ref="J70:N70" si="50">J68+J66+J57</f>
+        <f t="shared" ref="J70:N70" si="53">J68+J66+J57</f>
         <v>30848</v>
       </c>
       <c r="K70" s="15">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>33740</v>
       </c>
       <c r="L70" s="15">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>32310</v>
       </c>
       <c r="M70" s="15">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>29090</v>
       </c>
       <c r="N70" s="15">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>30958</v>
       </c>
       <c r="O70" s="15">
@@ -6431,7 +6581,10 @@
         <f>P68+P66+P57</f>
         <v>27926</v>
       </c>
-      <c r="Q70" s="17"/>
+      <c r="Q70" s="15">
+        <f>Q68+Q66+Q57</f>
+        <v>28715</v>
+      </c>
       <c r="R70" s="17"/>
       <c r="S70" s="17"/>
       <c r="T70" s="17"/>
